--- a/autoprogram/openvgp/names mapper.xlsx
+++ b/autoprogram/openvgp/names mapper.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\projects\autoprogram\autoprogram\vgpio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\projects\autoprogram\autoprogram\openvgp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1327D53-86D0-4383-9988-CD0D7B1DD94A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BEE60E-54FD-4299-A1E1-CBDE923CDD03}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>Tool.End Stock Removal</t>
   </si>
@@ -221,28 +221,52 @@
     <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.postpro.Vs</t>
   </si>
   <si>
-    <t>Tool.Set 1.Common Data.D0</t>
-  </si>
-  <si>
     <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.D0</t>
   </si>
   <si>
-    <t>Tool.Set 1.Common Data.sP2</t>
-  </si>
-  <si>
     <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.sP2</t>
   </si>
   <si>
     <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.sP1</t>
   </si>
   <si>
-    <t>Tool.Set 1.Common Data.sP1</t>
-  </si>
-  <si>
-    <t>Tool.Set 1.Common Data.pA</t>
-  </si>
-  <si>
     <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.pA</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1001.Helix Angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes2.helix.func_helix_angle</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1.Flute 1.Exit Radius</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.postpro.exitModus.ExitRadius</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1001.Flute 1001.Exit Radius</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes2.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.postpro.exitModus.ExitRadius</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes2.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.flute_Simple_Ext_.flute_Lw_X.flute_Simple_Choices.circ_land_width</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1001.Flute 1001.Circular Land Width</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Profile.pA</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Profile.D0</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Profile.sP1</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Profile.sP2</t>
   </si>
 </sst>
 </file>
@@ -670,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B2EC4B-F913-4D75-A9F6-A45AE9F236E1}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="90.42578125" style="3" customWidth="1"/>
@@ -687,34 +711,34 @@
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -955,6 +979,38 @@
       </c>
       <c r="B35" s="3" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1018,7 @@
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A6:B1048576 A1:B4">
+  <conditionalFormatting sqref="A1:B4 A6:B1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B5">

--- a/autoprogram/openvgp/names mapper.xlsx
+++ b/autoprogram/openvgp/names mapper.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\projects\autoprogram\autoprogram\openvgp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0gugale\projects\autoprogram\autoprogram\openvgp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BEE60E-54FD-4299-A1E1-CBDE923CDD03}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1178CBAF-6AB0-4306-9542-A7B3D2B625B0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
+    <workbookView xWindow="57480" yWindow="-9570" windowWidth="29040" windowHeight="15840" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
   <sheets>
     <sheet name="names mapper" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Tool.End Stock Removal</t>
   </si>
@@ -267,6 +267,54 @@
   </si>
   <si>
     <t>Tool.Set 1.Common Data.Profile.sP2</t>
+  </si>
+  <si>
+    <t>Blank.Profile.sA1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.sA1</t>
+  </si>
+  <si>
+    <t>Blank.Profile.sP1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.sP1</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Profile.D1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.D1</t>
+  </si>
+  <si>
+    <t>Tool.Set 2.OD Profile.D_2</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.D_2</t>
+  </si>
+  <si>
+    <t>Tool.Set 2.OD Profile.L_1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.L_2</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.L_1</t>
+  </si>
+  <si>
+    <t>Tool.Set 2.OD Profile.L_2</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes2.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.flute_Simple_Ext_.flute_Lw_X.flute_Simple_Choices.attackAngle</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1001.Flute 1001.Attack Angle</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1.Flute 1.Feedrate In</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.postpro.FeedIn.FeedIn</t>
   </si>
 </sst>
 </file>
@@ -350,10 +398,60 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -398,7 +496,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -694,14 +792,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B2EC4B-F913-4D75-A9F6-A45AE9F236E1}">
-  <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="90.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="240.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="90.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="240.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
@@ -709,7 +807,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>75</v>
       </c>
@@ -717,7 +815,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>74</v>
       </c>
@@ -725,7 +823,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>76</v>
       </c>
@@ -733,7 +831,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>77</v>
       </c>
@@ -741,291 +839,370 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>72</v>
       </c>
     </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:B38">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:B45">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B4 A6:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="A12:B1048576 A1:B4">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:B5">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A11:B1048576 A1:B9">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A10:B10">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:B10">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B9">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B9">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11:B11 A5:B9">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/autoprogram/openvgp/names mapper.xlsx
+++ b/autoprogram/openvgp/names mapper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0gugale\projects\autoprogram\autoprogram\openvgp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1178CBAF-6AB0-4306-9542-A7B3D2B625B0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7567BB7C-BCD3-485E-8033-832A71BC8598}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-9570" windowWidth="29040" windowHeight="15840" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
   <sheets>
     <sheet name="names mapper" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>Tool.End Stock Removal</t>
   </si>
@@ -315,6 +315,42 @@
   </si>
   <si>
     <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.postpro.FeedIn.FeedIn</t>
+  </si>
+  <si>
+    <t>Blank.Profile.D0</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.D0</t>
+  </si>
+  <si>
+    <t>Blank.Profile.D1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.D1</t>
+  </si>
+  <si>
+    <t>Blank.Profile.L</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.L</t>
+  </si>
+  <si>
+    <t>Blank.Coolant Holes.Group 1.Distance from center</t>
+  </si>
+  <si>
+    <t>Blank.Coolant Holes.Group 1.Holes Diameter</t>
+  </si>
+  <si>
+    <t>m_realBlank.Coolant_Holes.Hole_Type.Group.Group1.dist_from_center</t>
+  </si>
+  <si>
+    <t>m_realBlank.Coolant_Holes.Hole_Type.Group.Group1.holes_diameter</t>
+  </si>
+  <si>
+    <t>m_realBlank.Coolant_Holes.Hole_Type.Group.Group1.all_hole_helix.helix_hole.helix_hole1.helix_pas</t>
+  </si>
+  <si>
+    <t>Blank.Coolant Holes.Group 1.Helicoidal Holes.Helicoidal Holes.Lead</t>
   </si>
 </sst>
 </file>
@@ -401,7 +437,147 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -792,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B2EC4B-F913-4D75-A9F6-A45AE9F236E1}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="90.44140625" style="3" customWidth="1"/>
@@ -873,336 +1049,426 @@
     </row>
     <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>47</v>
+    <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:B45">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:B51">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A12:B1048576 A1:B4">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11:B1048576 A1:B9">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10:B10">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10:B10">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  <conditionalFormatting sqref="A18:B1048576 A1:B4">
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B9 A10 A13:B1048576">
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B9">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B9">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11:B11 A5:B9">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A10 A12:A1048576">
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:B9 A10 A13:B17">
+    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B10 A12:B1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11:B11">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/autoprogram/openvgp/names mapper.xlsx
+++ b/autoprogram/openvgp/names mapper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0gugale\projects\autoprogram\autoprogram\openvgp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7567BB7C-BCD3-485E-8033-832A71BC8598}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628E3E19-AE0B-4C63-8748-ADC0205CB1D7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
+    <workbookView xWindow="28680" yWindow="-9570" windowWidth="29040" windowHeight="15840" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
   <sheets>
     <sheet name="names mapper" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>Tool.End Stock Removal</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>Blank.Coolant Holes.Group 1.Helicoidal Holes.Helicoidal Holes.Lead</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Step 0.Point Relief.Relief Section 1.Edge Prolongation</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.endrelief_from_attribute.oneAttribute.oneAttribute1.extensionLength</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Step 0.Point Relief.Relief Section 1.Relief 1.Point Relief 1.dL End</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.endrelief_from_attribute.oneAttribute.oneAttribute1.od_relief.multi_relief_allmulti.multi_relief.multi_relief1.rel_intern.relief_op_complete.relief_op_complete1.corrLengthEnd</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Step 0.Point Relief.Relief Section 1.Relief 1.Point Relief 2.dL End</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.endrelief_from_attribute.oneAttribute.oneAttribute1.od_relief.multi_relief_allmulti.multi_relief.multi_relief1.rel_intern.relief_op_complete.relief_op_complete2.corrLengthEnd</t>
   </si>
 </sst>
 </file>
@@ -968,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B2EC4B-F913-4D75-A9F6-A45AE9F236E1}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="90.44140625" style="3" customWidth="1"/>
@@ -1399,6 +1417,30 @@
         <v>93</v>
       </c>
     </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:B51">
     <sortCondition ref="A1"/>

--- a/autoprogram/openvgp/names mapper.xlsx
+++ b/autoprogram/openvgp/names mapper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0gugale\projects\autoprogram\autoprogram\openvgp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628E3E19-AE0B-4C63-8748-ADC0205CB1D7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDE2C0E-7D21-4185-8A86-2639B0D6368F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-9570" windowWidth="29040" windowHeight="15840" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
+    <workbookView xWindow="57480" yWindow="-9570" windowWidth="29040" windowHeight="15840" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
   <sheets>
     <sheet name="names mapper" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>Tool.End Stock Removal</t>
   </si>
@@ -369,6 +369,30 @@
   </si>
   <si>
     <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.endrelief_from_attribute.oneAttribute.oneAttribute1.od_relief.multi_relief_allmulti.multi_relief.multi_relief1.rel_intern.relief_op_complete.relief_op_complete2.corrLengthEnd</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Profile.D</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Profile.L</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.D</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve.L</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flute &amp; Gash.Flute.Flute 1.Rake Angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.endmill_type.endmill_type1.n_Types.FluteGash.flute_from_attribute.n_Flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.flute.coreAndRakePart.func_rake_angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.endmill_type.endmill_type1.n_Types.FluteGash.flute_from_attribute.n_Flute.flute_op.num_flute</t>
+  </si>
+  <si>
+    <t>Unofficial.Number of Flutes</t>
   </si>
 </sst>
 </file>
@@ -986,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B2EC4B-F913-4D75-A9F6-A45AE9F236E1}">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="90.44140625" style="3" customWidth="1"/>
@@ -1066,447 +1090,479 @@
       </c>
     </row>
     <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>94</v>
+      <c r="A10" t="s">
+        <v>112</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>96</v>
+      <c r="A11" t="s">
+        <v>113</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>50</v>
+        <v>14</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>52</v>
+        <v>17</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>111</v>
       </c>
     </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:B51">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:B53">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A18:B1048576 A1:B4">
+  <conditionalFormatting sqref="A20:B1048576 A1:B4">
     <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B9 A10 A13:B1048576">
+  <conditionalFormatting sqref="A12 A15:B1048576 A1:B11">
     <cfRule type="duplicateValues" dxfId="20" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="A14:B14">
     <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="A14:B14">
     <cfRule type="duplicateValues" dxfId="18" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B9">
+  <conditionalFormatting sqref="B6:B11">
     <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B9">
+  <conditionalFormatting sqref="B6:B11">
     <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A10 A12:A1048576">
+  <conditionalFormatting sqref="A14:A1048576 A1:A12">
     <cfRule type="duplicateValues" dxfId="15" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:B9 A10 A13:B17">
+  <conditionalFormatting sqref="A12 A15:B19 A5:B11">
     <cfRule type="duplicateValues" dxfId="14" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10">
+  <conditionalFormatting sqref="A12">
     <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10">
+  <conditionalFormatting sqref="A12">
     <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
+  <conditionalFormatting sqref="B12">
     <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
+  <conditionalFormatting sqref="B12">
     <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B10 A12:B1048576">
+  <conditionalFormatting sqref="A14:B1048576 A1:B12">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
+  <conditionalFormatting sqref="B13">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
+  <conditionalFormatting sqref="B13">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11:B11">
+  <conditionalFormatting sqref="A13:B13">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1048576">

--- a/autoprogram/openvgp/names mapper.xlsx
+++ b/autoprogram/openvgp/names mapper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0gugale\projects\autoprogram\autoprogram\openvgp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDE2C0E-7D21-4185-8A86-2639B0D6368F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40E3D39-1CB7-49BC-B208-C46778BB42AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-9570" windowWidth="29040" windowHeight="15840" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>Tool.End Stock Removal</t>
   </si>
@@ -393,6 +393,18 @@
   </si>
   <si>
     <t>Unofficial.Number of Flutes</t>
+  </si>
+  <si>
+    <t>Blank.Profile.fL</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.fL</t>
+  </si>
+  <si>
+    <t>Blank.Profile.fD</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.fD</t>
   </si>
 </sst>
 </file>
@@ -479,7 +491,387 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="60">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1010,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B2EC4B-F913-4D75-A9F6-A45AE9F236E1}">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="90.44140625" style="3" customWidth="1"/>
@@ -1139,431 +1531,465 @@
     </row>
     <row r="16" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>50</v>
+        <v>14</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>52</v>
+        <v>17</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B62" s="3" t="s">
         <v>118</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:B53">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:B55">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A20:B1048576 A1:B4">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12 A15:B1048576 A1:B11">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+  <conditionalFormatting sqref="A22:B1048576 A1:B4">
+    <cfRule type="duplicateValues" dxfId="59" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12 A1:B11 A15:B15 A17:B1048576">
+    <cfRule type="duplicateValues" dxfId="58" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:B14">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:B14">
-    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B11">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B11">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:A1048576 A1:A12">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12 A15:B19 A5:B11">
-    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14:A15 A1:A12 A17:A1048576">
+    <cfRule type="duplicateValues" dxfId="53" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12 A5:B11 A15:B15 A17:B21">
+    <cfRule type="duplicateValues" dxfId="52" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:B1048576 A1:B12">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B12 A14:B15 A17:B1048576">
+    <cfRule type="duplicateValues" dxfId="47" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B13">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B15 A17:B1048576">
+    <cfRule type="duplicateValues" dxfId="38" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:B16">
+    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:B16">
+    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:B16">
+    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:B16">
+    <cfRule type="duplicateValues" dxfId="33" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/autoprogram/openvgp/names mapper.xlsx
+++ b/autoprogram/openvgp/names mapper.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0gugale\projects\autoprogram\autoprogram\openvgp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Common\MTI_Production-Engineering-Team\AUTOPROGRAM\autoprogram\autoprogram\openvgp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40E3D39-1CB7-49BC-B208-C46778BB42AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8060A063-D058-4566-B6F8-17ACE7C27397}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-9570" windowWidth="29040" windowHeight="15840" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
     <t>Tool.End Stock Removal</t>
   </si>
@@ -405,6 +405,48 @@
   </si>
   <si>
     <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.fD</t>
+  </si>
+  <si>
+    <t>Blank.Profile.htA</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.htA</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.endmill_type.endmill_type2.n_Types.relieves.endrelief_from_attribute.n_EndRelief.multi_relief_allmulti.multi_relief.multi_relief1.rel_intern.relief_op_complete.relief_op_complete1.corrLengthStart</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Relieves.End Relief.End Relief 1.End Relief 1.Depth Past Center.Tooth 2, Tooth 3</t>
+  </si>
+  <si>
+    <t>Blank.Profile.sD</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve.sD</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Reliefs.End Relief.End Relief 1.End Relief 1.Depth Past Center.Tooth 2, Tooth 4</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1.Flute 1 (Output).Rake Angle</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Step 0 (Point).Gash.Gash 1.Gash Angle</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Flutes.Flute 1.Flute 101.Attack Angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi101.flute_Simple_Ext_.flute_Lw_X.flute_Simple_Choices.attackAngle</t>
+  </si>
+  <si>
+    <t>Tool.Set 1.Common Data.Step 0 (Point).Gash.Gash 101.Gash Angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.drill_straightgash_group.drill_straightgash_group.drill_straightgash_group.gash_one_multi.gash_one_multi1.eghGashAngle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.drill_straightgash_group.drill_straightgash_group.drill_straightgash_group.gash_one_multi.gash_one_multi101.eghGashAngle</t>
   </si>
 </sst>
 </file>
@@ -469,21 +511,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -491,517 +534,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1402,11 +935,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B2EC4B-F913-4D75-A9F6-A45AE9F236E1}">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="90.44140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="240.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="93.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="240.6640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1418,581 +951,588 @@
       </c>
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+    <row r="22" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+    <row r="23" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B45" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B51" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B52" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B53" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B55" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B56" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B57" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B58" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B59" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B60" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B61" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B63" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B65" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B66" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B67" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B68" s="5" t="s">
         <v>118</v>
       </c>
     </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:B55">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:B61">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A22:B1048576 A1:B4">
-    <cfRule type="duplicateValues" dxfId="59" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12 A1:B11 A15:B15 A17:B1048576">
-    <cfRule type="duplicateValues" dxfId="58" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:B14">
-    <cfRule type="duplicateValues" dxfId="57" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:B14">
-    <cfRule type="duplicateValues" dxfId="56" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B11">
-    <cfRule type="duplicateValues" dxfId="55" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B11">
-    <cfRule type="duplicateValues" dxfId="54" priority="27"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A14:A15 A1:A12 A17:A1048576">
-    <cfRule type="duplicateValues" dxfId="53" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12 A5:B11 A15:B15 A17:B21">
-    <cfRule type="duplicateValues" dxfId="52" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="51" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="50" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="49" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="48" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B12 A14:B15 A17:B1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="46" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="45" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="43" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="42" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="41" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="40" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:B13">
-    <cfRule type="duplicateValues" dxfId="39" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B15 A17:B1048576">
-    <cfRule type="duplicateValues" dxfId="38" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16:B16">
-    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16:B16">
-    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16:B16">
-    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16:B16">
-    <cfRule type="duplicateValues" dxfId="33" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
